--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46192.65625</v>
+        <v>46192.66666666666</v>
       </c>
     </row>
     <row r="14">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>8.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>8.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="O4" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>8.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>1.31</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.31</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>9.199999999999999</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>8.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>8.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.36</v>
+        <v>3.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.31</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
         <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>8.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="P12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>8.85</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.87</v>
+        <v>1.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>8.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>4.92</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>8.85</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3.68</v>
+        <v>5.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.62</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="O5" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="P5" t="n">
-        <v>8.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>3.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>4.92</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>4.62</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.87</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>4.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.62</v>
+        <v>4.92</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>8.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>5.3</v>
+        <v>3.68</v>
       </c>
       <c r="P5" t="n">
-        <v>9.199999999999999</v>
+        <v>4.62</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>8.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.82</v>
+        <v>8.85</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>3.87</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.92</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>8.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>9.199999999999999</v>
+        <v>4.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="O4" t="n">
-        <v>5.7</v>
+        <v>3.68</v>
       </c>
       <c r="P4" t="n">
-        <v>8.85</v>
+        <v>4.62</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O5" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P5" t="n">
-        <v>4.62</v>
+        <v>4.92</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>8.85</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>4.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>3.68</v>
+        <v>5.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.62</v>
+        <v>8.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.58</v>
+        <v>3.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.92</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>8.85</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.92</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,14 +1997,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>1.78</v>
       </c>
       <c r="O10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P10" t="n">
         <v>4.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>4.62</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="O4" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>8.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.87</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.31</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>4.92</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
-        <v>3.68</v>
+        <v>5.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.62</v>
+        <v>8.85</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>8.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>3.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.62</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>4.92</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>1.64</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>4.62</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O12" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>8.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>4.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>4.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>4.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>8.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
         <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.62</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>4.62</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>8.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>9.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>8.85</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>4.92</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.64</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P12" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -734,40 +734,40 @@
         <v>4.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC2" t="n">
         <v>1.93</v>
@@ -776,13 +776,13 @@
         <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>8.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="P9" t="n">
-        <v>4.92</v>
+        <v>8.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>1.58</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>4.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.87</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,34 +2324,34 @@
         <v>4.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
         <v>1.77</v>
@@ -2360,19 +2360,19 @@
         <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>8.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.6</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="S5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.55</v>
+        <v>2.21</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S7" t="n">
         <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AD7" t="n">
         <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>3.87</v>
       </c>
       <c r="O9" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>8.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>4.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>4.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -2033,28 +2033,28 @@
         <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="U11" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="V11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.38</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>4.62</v>
+        <v>4.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U12" t="n">
         <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
         <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.6</v>
+        <v>2.91</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>8.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>8.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>3.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>4.62</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.21</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
         <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="U10" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="V10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.38</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="O11" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>9.199999999999999</v>
+        <v>4.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P12" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
         <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.82</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.91</v>
+        <v>5.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O6" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="P6" t="n">
-        <v>8.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.73</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AB6" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.1</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P8" t="n">
         <v>4.2</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.87</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>8.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.55</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="O10" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>9.199999999999999</v>
+        <v>4.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.04</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P11" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
         <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
         <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.64</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.62</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.21</v>
+        <v>2.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>1.27</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>8.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.6</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>2.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
         <v>3.1</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
         <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.34</v>
+        <v>2.04</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.31</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>8.85</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.73</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AG9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.92</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.74</v>
+        <v>3.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.38</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O11" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>4.62</v>
+        <v>4.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
         <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
         <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.91</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="U12" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="V12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.38</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>8.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.62</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.21</v>
+        <v>3.77</v>
       </c>
       <c r="R5" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
         <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
         <v>1.94</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.19</v>
+        <v>1.83</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>5.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.87</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>8.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.55</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>2.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,61 +1679,61 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.91</v>
+        <v>5.55</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.38</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
         <v>2.05</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>2.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.6</v>
+        <v>3.89</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>4.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P11" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
         <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
         <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.31</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>9.199999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>2.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.64</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>4.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.77</v>
+        <v>2.91</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
-        <v>5.55</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="P7" t="n">
-        <v>8.85</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R7" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.55</v>
+        <v>3.77</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.31</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.89</v>
+        <v>5.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.42</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.02</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
         <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
         <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.21</v>
+        <v>3.89</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>8.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.91</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>4.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.22</v>
+        <v>2.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>3.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>5.55</v>
       </c>
       <c r="P4" t="n">
-        <v>4.92</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.91</v>
+        <v>3.77</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>4.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>8.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.6</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>4.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.55</v>
+        <v>2.21</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.31</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AE9" t="n">
         <v>1.08</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.64</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>4.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.21</v>
+        <v>3.89</v>
       </c>
       <c r="R10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.89</v>
+        <v>5.55</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.42</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.34</v>
-      </c>
       <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.02</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="O12" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>8.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.25</v>
       </c>
-      <c r="T12" t="n">
+      <c r="Z12" t="n">
         <v>3.28</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.35</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.33</v>
+        <v>3.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>5.55</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>3.89</v>
       </c>
       <c r="R4" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.54</v>
+        <v>3.44</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.75</v>
+        <v>1.34</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>4.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.77</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="U5" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>4.92</v>
+        <v>2.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1397,28 +1397,28 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.21</v>
+        <v>5.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>2.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.04</v>
+        <v>1.14</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>5.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.89</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.02</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.12</v>
+        <v>4.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.44</v>
+        <v>2.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>3.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>4.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.55</v>
+        <v>2.21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.31</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AE11" t="n">
         <v>1.08</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>2.31</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O2" t="n">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>2.58</v>
@@ -743,7 +743,7 @@
         <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U2" t="n">
         <v>1.97</v>
@@ -752,16 +752,16 @@
         <v>1.77</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.4</v>
+        <v>5.92</v>
       </c>
       <c r="AA2" t="n">
         <v>1.4</v>
@@ -770,19 +770,19 @@
         <v>2.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
         <v>1.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.89</v>
+        <v>3.76</v>
       </c>
       <c r="R4" t="n">
         <v>2.15</v>
@@ -1061,7 +1061,7 @@
         <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
         <v>2.99</v>
@@ -1097,7 +1097,7 @@
         <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
         <v>1.95</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>4.92</v>
+        <v>4.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.36</v>
+        <v>1.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.82</v>
+        <v>5.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1397,28 +1397,28 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
         <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="P7" t="n">
-        <v>8.85</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>2.59</v>
@@ -1541,19 +1541,19 @@
         <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V7" t="n">
         <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
         <v>4.35</v>
@@ -1562,7 +1562,7 @@
         <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AC7" t="n">
         <v>2.33</v>
@@ -1571,7 +1571,7 @@
         <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
         <v>1.95</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,61 +1679,61 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>4.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.77</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
         <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
         <v>1.94</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>2.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.55</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.94</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG9" t="n">
         <v>2.05</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>3.83</v>
       </c>
       <c r="O10" t="n">
-        <v>5.55</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>3.77</v>
       </c>
       <c r="R10" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.54</v>
+        <v>3.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.75</v>
+        <v>1.24</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.68</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.62</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>4.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.78</v>
+        <v>5.16</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>1.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="P13" t="n">
-        <v>3.44</v>
+        <v>3.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.09</v>
+        <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.7</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3.96</v>
+        <v>5.3</v>
       </c>
       <c r="P6" t="n">
-        <v>5.3</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.22</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>9.550000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>3.76</v>
       </c>
       <c r="R7" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.35</v>
+        <v>3.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.15</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.83</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>4.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>5.16</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>5.55</v>
       </c>
       <c r="R11" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.16</v>
+        <v>3.94</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB11" t="n">
         <v>2.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.16</v>
+        <v>1.51</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="P12" t="n">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.55</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.83</v>
+        <v>1.22</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.77</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.24</v>
+        <v>4.35</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.24</v>
+        <v>3.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="O5" t="n">
-        <v>5.5</v>
+        <v>3.96</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="R5" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
         <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>9.550000000000001</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>3.76</v>
       </c>
       <c r="R6" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.15</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U7" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>5.16</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P8" t="n">
-        <v>4.72</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>5.55</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
         <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>2.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>3.26</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.79</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
-        <v>2.85</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>4.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.27</v>
+        <v>2.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.16</v>
+        <v>3.83</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.55</v>
+        <v>3.77</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.94</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>2.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>5.3</v>
+        <v>4.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
         <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P4" t="n">
         <v>5.3</v>
       </c>
-      <c r="P4" t="n">
-        <v>9.550000000000001</v>
-      </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="R4" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>5.3</v>
+        <v>4.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.76</v>
+        <v>4.41</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.16</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.59</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.55</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
         <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="U8" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.94</v>
+        <v>4.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.31</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.14</v>
+        <v>3.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.16</v>
+        <v>4.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.31</v>
+        <v>4.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.77</v>
+        <v>4.59</v>
       </c>
       <c r="R11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.1</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.62</v>
+        <v>3.09</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>4.72</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>3.76</v>
       </c>
       <c r="R12" t="n">
         <v>2.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
         <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15" t="n">

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -734,22 +734,22 @@
         <v>3.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
         <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -758,28 +758,28 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.92</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG2" t="n">
         <v>2.66</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.96</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>5.3</v>
+        <v>2.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.05</v>
+        <v>3.01</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.46</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>4.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.41</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.98</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.79</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4.59</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.28</v>
+        <v>3.94</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.27</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>3.09</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>3.76</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>3.27</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.44</v>
+        <v>2.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.16</v>
+        <v>3.31</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.57</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.7</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
         <v>5.3</v>
@@ -1847,16 +1847,16 @@
         <v>9.550000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="S9" t="n">
         <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
         <v>2.28</v>
@@ -1877,7 +1877,7 @@
         <v>4.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
         <v>2.27</v>
@@ -1892,7 +1892,7 @@
         <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
         <v>1.75</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>4.72</v>
+        <v>4.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
         <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
         <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.29</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.09</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.76</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.18</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.35</v>
+        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.79</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.47</v>
+        <v>4.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.27</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>3.6</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>4.32</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.59</v>
+        <v>3.76</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>2.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.94</v>
+        <v>3.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.09</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.76</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>2.29</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>5.3</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>9.550000000000001</v>
+        <v>2.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>3.01</v>
       </c>
       <c r="R9" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="S9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK9" t="n">
-        <v>3.6</v>
+        <v>1.46</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.52</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>4.85</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>4.41</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.29</v>
+        <v>1.24</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>1.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P11" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q11" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,43 +2315,43 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>4.59</v>
       </c>
       <c r="R12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.16</v>
+        <v>3.94</v>
       </c>
       <c r="AA12" t="n">
         <v>1.7</v>
@@ -2360,35 +2360,35 @@
         <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1046,61 +1046,61 @@
         <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>9.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>4.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.31</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.7</v>
+        <v>1.98</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.05</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>4.59</v>
       </c>
       <c r="R6" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.98</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.29</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>4.05</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>4.59</v>
       </c>
       <c r="R5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.98</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.29</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.09</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>4.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
         <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>3.09</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="P8" t="n">
-        <v>4.85</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.05</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.3</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.21</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.39</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.46</v>
+        <v>2.29</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="O10" t="n">
-        <v>5.3</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>9.550000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P11" t="n">
-        <v>4.32</v>
+        <v>2.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK12" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R2" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -761,28 +761,28 @@
         <v>1.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF2" t="n">
         <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.16</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.59</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.94</v>
+        <v>3.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>4.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.41</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.88</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.42</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>5.45</v>
       </c>
       <c r="P7" t="n">
-        <v>4.05</v>
+        <v>9.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.57</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.09</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.52</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.85</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.05</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.32</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.29</v>
+        <v>1.34</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.71</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>2.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.36</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.39</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
         <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,77 +2318,77 @@
         <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P12" t="n">
-        <v>9.550000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK12" t="n">
         <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>3.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>5.45</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>9.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>9.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK7" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>4.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.75</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.94</v>
+        <v>3.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.77</v>
+        <v>3.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.23</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>5.45</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>9.65</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.25</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AE4" t="n">
         <v>1.11</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1238,28 +1238,28 @@
         <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.47</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P6" t="n">
-        <v>4.82</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>5.45</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>9.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>3.62</v>
+        <v>5.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>1.52</v>
       </c>
       <c r="O9" t="n">
         <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.15</v>
+        <v>2.26</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>4.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.4</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.42</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
         <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>3.94</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.92</v>
+        <v>3.47</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.69</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1238,28 +1238,28 @@
         <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>3.47</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>3.62</v>
+        <v>5.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>9.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK7" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.52</v>
+        <v>4.75</v>
       </c>
       <c r="O9" t="n">
         <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>4.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.26</v>
+        <v>1.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.94</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>5.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>9.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.06</v>
+        <v>2.57</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T12" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.46</v>
+        <v>3.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -737,7 +737,7 @@
         <v>2.11</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
         <v>1.2</v>
@@ -776,7 +776,7 @@
         <v>1.78</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
         <v>1.4</v>
@@ -798,7 +798,7 @@
         <v>1.19</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,43 +1043,43 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
         <v>1.95</v>
@@ -1088,19 +1088,19 @@
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.27</v>
+        <v>2.77</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.26</v>
       </c>
-      <c r="O6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z6" t="n">
-        <v>3.92</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>9.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
         <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>4.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>5.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.12</v>
+        <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.75</v>
+        <v>2.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="R9" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>1.33</v>
@@ -1859,43 +1859,43 @@
         <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
         <v>1.42</v>
       </c>
       <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.67</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="AB10" t="n">
         <v>2.15</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AC10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.16</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
         <v>1.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.23</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>5.45</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>9.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2480,37 +2480,37 @@
         <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
         <v>1.66</v>
@@ -2519,19 +2519,19 @@
         <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.7</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.29</v>
-      </c>
       <c r="R4" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.31</v>
+        <v>2.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.94</v>
+        <v>3.35</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
         <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
         <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.25</v>
       </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="AE7" t="n">
         <v>1.11</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>5.16</v>
+        <v>9.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.68</v>
+        <v>4.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>5.55</v>
+        <v>3.84</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>5.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.51</v>
+        <v>2.87</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,43 +2315,43 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>4.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
         <v>1.95</v>
@@ -2360,19 +2360,19 @@
         <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>3.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="S4" t="n">
         <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
@@ -1076,31 +1076,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>3.35</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.44</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>5.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
         <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>9.65</v>
+        <v>4.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="R8" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.52</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>3.31</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>5.16</v>
+        <v>9.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.68</v>
+        <v>4.52</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>5.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U11" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.75</v>
+        <v>2.51</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.29</v>
-      </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
         <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>9.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.24</v>
+        <v>4.52</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK5" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.2</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>4.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>5.16</v>
+        <v>4.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.7</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.29</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.31</v>
+        <v>2.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.94</v>
+        <v>3.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1871,31 +1871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>9.65</v>
+        <v>4.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.52</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="S11" t="n">
         <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
@@ -2189,31 +2189,31 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.51</v>
+        <v>2.77</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>5.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.12</v>
+        <v>3.68</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.75</v>
+        <v>2.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -728,28 +728,28 @@
         <v>1.66</v>
       </c>
       <c r="O2" t="n">
-        <v>4.2</v>
+        <v>3.93</v>
       </c>
       <c r="P2" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>1.2</v>
@@ -761,13 +761,13 @@
         <v>1.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AA2" t="n">
         <v>1.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AC2" t="n">
         <v>1.98</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.54</v>
+        <v>4.12</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.14</v>
+        <v>4.79</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,61 +1043,61 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG4" t="n">
         <v>1.93</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="P5" t="n">
-        <v>9.65</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>1.7</v>
@@ -1223,7 +1223,7 @@
         <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V5" t="n">
         <v>1.54</v>
@@ -1235,7 +1235,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>4.52</v>
@@ -1247,7 +1247,7 @@
         <v>2.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
         <v>1.48</v>
@@ -1256,10 +1256,10 @@
         <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.31</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
         <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>4.37</v>
+        <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
         <v>1.95</v>
@@ -1565,19 +1565,19 @@
         <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.94</v>
+        <v>1.49</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1871,47 +1871,47 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.34</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.67</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="AB10" t="n">
         <v>2.15</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AC10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.16</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>2.08</v>
@@ -2333,7 +2333,7 @@
         <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U12" t="n">
         <v>2.5</v>
@@ -2345,16 +2345,16 @@
         <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
         <v>1.99</v>
@@ -2363,7 +2363,7 @@
         <v>2.87</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
         <v>1.11</v>
@@ -2372,7 +2372,7 @@
         <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.31</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>8.710000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="R5" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U5" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z5" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK5" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="R6" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.77</v>
+        <v>3.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>5.55</v>
       </c>
       <c r="P7" t="n">
-        <v>2.73</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.49</v>
+        <v>3.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>4.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.17</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.93</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>2.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.51</v>
+        <v>3.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.35</v>
+        <v>1.93</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
         <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
         <v>1.93</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
         <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S12" t="n">
         <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>1.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U13" t="n">
         <v>2.47</v>
@@ -2525,7 +2525,7 @@
         <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
         <v>1.6</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.31</v>
+        <v>1.26</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>5.55</v>
       </c>
       <c r="P4" t="n">
-        <v>2.73</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.1</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.49</v>
+        <v>3.34</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.19</v>
+        <v>3.45</v>
       </c>
       <c r="R5" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
         <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>4.75</v>
       </c>
       <c r="O7" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
@@ -1553,31 +1553,31 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>3.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
         <v>1.93</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.17</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.93</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>2.17</v>
       </c>
       <c r="R12" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.77</v>
+        <v>3.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.08</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK4" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.73</v>
+        <v>4.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="U6" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.3</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="P8" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.52</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.3</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>1.93</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.24</v>
+        <v>1.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.77</v>
       </c>
-      <c r="U10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.67</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.1</v>
+        <v>3.34</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.31</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="AC7" t="n">
         <v>2.77</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>5.55</v>
+        <v>3.44</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.3</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.34</v>
+        <v>1.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
         <v>1.93</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.75</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>2.19</v>
       </c>
       <c r="R10" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
         <v>1.42</v>
       </c>
       <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.07</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,43 +2315,43 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
         <v>1.95</v>
@@ -2360,19 +2360,19 @@
         <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="O2" t="n">
         <v>3.93</v>
       </c>
       <c r="P2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.18</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.83</v>
+        <v>5.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF2" t="n">
         <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,28 +893,28 @@
         <v>1.74</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.79</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V3" t="n">
         <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
@@ -926,13 +926,13 @@
         <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.05</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>8.710000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.52</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG4" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.34</v>
+        <v>2.24</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>2.94</v>
       </c>
       <c r="R7" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.2</v>
+        <v>3.38</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>5.55</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.24</v>
+        <v>3.7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,55 +1997,55 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.19</v>
+        <v>3.92</v>
       </c>
       <c r="R10" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
         <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
         <v>1.08</v>
@@ -2054,7 +2054,7 @@
         <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.7</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.31</v>
+        <v>2.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.73</v>
+        <v>4.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.49</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
         <v>3.5</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.27</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.2</v>
       </c>
       <c r="S13" t="n">
         <v>1.29</v>
@@ -2501,7 +2501,7 @@
         <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
@@ -2519,19 +2519,19 @@
         <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="S4" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>3.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
         <v>3.5</v>
       </c>
-      <c r="P5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
         <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T7" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
         <v>1.95</v>
@@ -1568,16 +1568,16 @@
         <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="O8" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>8.710000000000001</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>9</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
         <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD9" t="n">
         <v>1.4</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.7</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.92</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
         <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.65</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.15</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>3.18</v>
+        <v>5.55</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.92</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.34</v>
+        <v>3.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
         <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U6" t="n">
         <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.24</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="S7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
         <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
         <v>1.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,58 +1679,58 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.3</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,43 +1997,43 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
         <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.49</v>
       </c>
       <c r="AA10" t="n">
         <v>1.95</v>
@@ -2042,19 +2042,19 @@
         <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
         <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.49</v>
+        <v>3.74</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>5.55</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.92</v>
+        <v>2.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
         <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,55 +1679,55 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,43 +1838,43 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q9" t="n">
         <v>4.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.2</v>
       </c>
       <c r="R9" t="n">
         <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T9" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
         <v>1.95</v>
@@ -1883,13 +1883,13 @@
         <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
         <v>1.75</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.94</v>
+        <v>3.92</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
         <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.65</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.15</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,58 +2315,58 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.95</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O2" t="n">
-        <v>3.93</v>
+        <v>4.3</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
         <v>2.63</v>
@@ -746,13 +746,13 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,19 +761,19 @@
         <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="n">
         <v>1.3</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,61 +884,61 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.12</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>4.94</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.37</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
         <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
         <v>1.9</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
         <v>1.2</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>8.710000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="R4" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.5</v>
+        <v>3.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK4" t="n">
-        <v>3.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1.65</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AE5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.1</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>3.37</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.3</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.15</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.49</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>4.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.03</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.92</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>3.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.65</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.27</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,58 +2315,58 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>2.74</v>
+        <v>3.31</v>
       </c>
       <c r="U12" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
         <v>3.5</v>
@@ -2486,22 +2486,22 @@
         <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="V13" t="n">
         <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
@@ -2510,19 +2510,19 @@
         <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
         <v>1.17</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>8.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.33</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>3.27</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.12</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>3.37</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>8.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>3.33</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3.27</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,34 +1361,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.46</v>
+        <v>3.06</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
@@ -1397,28 +1397,28 @@
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA8" t="n">
         <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.25</v>
       </c>
-      <c r="O10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.17</v>
+        <v>1.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,28 +2156,28 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="S11" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V11" t="n">
         <v>1.38</v>
@@ -2186,25 +2186,25 @@
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
         <v>1.11</v>
@@ -2213,7 +2213,7 @@
         <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.33</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T5" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
         <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.88</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>4.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AK7" t="n">
         <v>2.02</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.68</v>
+        <v>3.83</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>4.46</v>
       </c>
       <c r="R8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
         <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.05</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
         <v>3.2</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AD9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.1</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.83</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.46</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>2.86</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.25</v>
+        <v>3.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>2.87</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="R12" t="n">
-        <v>2.49</v>
+        <v>2.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK12" t="n">
-        <v>3.17</v>
+        <v>1.36</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.25</v>
       </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.37</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.68</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AB5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.88</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>2.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>4.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AK6" t="n">
         <v>2.02</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="P7" t="n">
-        <v>4.55</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.02</v>
+        <v>3.17</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.83</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.46</v>
+        <v>3.06</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.05</v>
@@ -1715,28 +1715,28 @@
         <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.5</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.07</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.1</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>3.37</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="O10" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.17</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>3.33</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.31</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
         <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.87</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.33</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -728,61 +728,61 @@
         <v>1.61</v>
       </c>
       <c r="O2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF2" t="n">
         <v>1.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK2" t="n">
         <v>2.15</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.94</v>
+        <v>4.72</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>2.74</v>
+        <v>2.41</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.83</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>8.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.46</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="S4" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>3.88</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>2.21</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S5" t="n">
         <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
         <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
         <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>2.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.17</v>
+        <v>2.07</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.61</v>
+        <v>2.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.55</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.3</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.1</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>5.25</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T7" t="n">
         <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
         <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC7" t="n">
         <v>2.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.06</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
         <v>2.07</v>
@@ -1697,47 +1697,47 @@
         <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>8.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.27</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.68</v>
+        <v>3.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.37</v>
+        <v>2.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,58 +1997,58 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>4.8</v>
+        <v>5.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
         <v>3.31</v>
       </c>
       <c r="U10" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
         <v>1.75</v>
@@ -2070,7 +2070,7 @@
         <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.07</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AC11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.4</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.68</v>
+        <v>3.58</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>4.35</v>
       </c>
       <c r="R12" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.05</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O13" t="n">
         <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
         <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
         <v>2.2</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
         <v>1.91</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -702,26 +702,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '52', '83']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '89']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46192.58333333334</v>
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '37']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '31']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46192.60416666666</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>8.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.88</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="O5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.5</v>
       </c>
-      <c r="P5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.1</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.07</v>
+        <v>1.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>5.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>2.77</v>
+        <v>3.31</v>
       </c>
       <c r="U6" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>9.050000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="R7" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="S7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.07</v>
+        <v>2.61</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.69</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.68</v>
+        <v>3.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>4.35</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>5.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>3.31</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
         <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.58</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>8.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.35</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>2.98</v>
+        <v>2.43</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>3.88</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>3.58</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>4.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.24</v>
+        <v>4.35</v>
       </c>
       <c r="R4" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
         <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '36']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '64']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
         <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46192.65625</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,16 +1170,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1191,118 +1191,118 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.65</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.46</v>
+        <v>8.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.39</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>['90+3', '90+4']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.45</v>
+        <v>3.88</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46192.65625</v>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1350,118 +1350,118 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="P6" t="n">
-        <v>5.35</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T6" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>['52', '56', '62', '84']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46192.65625</v>
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '53', '55', '64', '90+1']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '86']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46192.65625</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>9.050000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.11</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AF8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['37', '84']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46192.65625</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,25 +1806,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1834,68 +1834,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.58</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD9" t="n">
         <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
         <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46192.65625</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,139 +1965,139 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S10" t="n">
         <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.69</v>
+        <v>3.39</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '51']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '63']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46192.65625</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>5.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U11" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
         <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65', '67', '79']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.18</v>
+        <v>2.24</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46192.65625</v>
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>8.9</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.62</v>
+        <v>3.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '48']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.88</v>
+        <v>1.36</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46192.65625</v>
@@ -2451,26 +2451,26 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '76']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46192.66666666666</v>

--- a/jogos_2026-06-19.xlsx
+++ b/jogos_2026-06-19.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.58</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AA4" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AD4" t="n">
         <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['24', '36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['15', '64']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
         <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1125,25 +1125,25 @@
         <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.24</v>
+        <v>0.92</v>
       </c>
       <c r="AS4" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AT4" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46192.65625</v>
@@ -1170,136 +1170,136 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['37', '84']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['90+3', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>8</v>
-      </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.71</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AS5" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="AT5" t="n">
         <v>41</v>
@@ -1329,139 +1329,139 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['30', '51']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['18', '63']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['52', '56', '62', '84']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>15</v>
-      </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.83</v>
+        <v>0.79</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.33</v>
+        <v>0.68</v>
       </c>
       <c r="AS6" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="AT6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46192.65625</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['90+3', '90+4']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['22', '53', '55', '64', '90+1']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['48', '86']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3</v>
-      </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AP7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.14</v>
+        <v>3.71</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AS7" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AT7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46192.65625</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,31 +1647,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>2.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1715,71 +1715,71 @@
         <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC8" t="n">
         <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '53', '55', '64', '90+1']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['37', '84']</t>
+          <t>['48', '86']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.18</v>
+        <v>2.07</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>3.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.54</v>
+        <v>0.79</v>
       </c>
       <c r="AS8" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="AT8" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46192.65625</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,31 +1806,31 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S9" t="n">
         <v>1.36</v>
@@ -1859,37 +1859,37 @@
         <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.04</v>
+        <v>3.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
         <v>1.75</v>
@@ -1899,46 +1899,46 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '48']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP9" t="n">
         <v>14</v>
       </c>
-      <c r="AP9" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.92</v>
+        <v>1.78</v>
       </c>
       <c r="AS9" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="AT9" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46192.65625</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1980,13 +1980,13 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>3.58</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="R10" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['30', '51']</t>
+          <t>['24', '36']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['18', '63']</t>
+          <t>['15', '64']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AO10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.79</v>
+        <v>1.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.68</v>
+        <v>2.24</v>
       </c>
       <c r="AS10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AT10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46192.65625</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,31 +2283,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.61</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U12" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>['52', '56', '62', '84']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR12" t="n">
         <v>1.33</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>['24', '48']</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AS12" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="AT12" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46192.65625</v>
